--- a/results/06_model_evaluation/05_ALL_model_eval.xlsx
+++ b/results/06_model_evaluation/05_ALL_model_eval.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7827777918629683</v>
+        <v>0.7830138502042437</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01875913928122007</v>
+        <v>0.01871381086800399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.127235033139615</v>
+        <v>0.1269362344566973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03014154041782496</v>
+        <v>0.03004361656874081</v>
       </c>
     </row>
     <row r="3">
@@ -502,40 +502,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7950423734525505</v>
+        <v>0.7914604990850014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.022906276421525</v>
+        <v>0.02177196714317657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1921294753460224</v>
+        <v>0.1983569539223893</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04173421597947816</v>
+        <v>0.0418411119299538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7749474054256495</v>
+        <v>0.6846025597459205</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03936580996781421</v>
+        <v>0.02015002765830965</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1888878873417933</v>
+        <v>0.089148033989234</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04243115752518334</v>
+        <v>0.01336735536260493</v>
       </c>
     </row>
     <row r="5">
@@ -546,74 +546,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>logreg_l2</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6846025597459205</v>
+        <v>0.8446039484260537</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02015002765830965</v>
+        <v>0.0208459627145983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.089148033989234</v>
+        <v>0.3408291022517788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01336735536260493</v>
+        <v>0.02388852541442163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>logreg_l2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8446039484260537</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0208459627145983</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3408291022517788</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02388852541442163</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8193635515576089</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02336584643623031</v>
+        <v>0.01830461526364529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3434883471190159</v>
+        <v>0.1305084174604524</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02827551939034324</v>
+        <v>0.01322728173796852</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7436214385423241</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01760657006189662</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="E8" t="n">
-        <v>0.120027452177884</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01573639136082546</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,190 +646,190 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7803300993572464</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02240333750729686</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1395906583983687</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01473078343769954</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7671712109690169</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01692627218546185</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1433738303844752</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01829340997248071</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>logreg_l2</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.740204074741885</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>logreg_l2_scaled</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.7830138502042437</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.01871381086800399</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.1269362344566973</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.03004361656874081</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>gradboost</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7950796888840379</v>
+        <v>0.7865382823285895</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01567424950546039</v>
+        <v>0.02714716402184768</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2118479711579678</v>
+        <v>0.1635667006523789</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02546531256831987</v>
+        <v>0.04077642148042858</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>logreg_l2</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.7735886016058289</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.03016234961409352</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.1643278581485317</v>
       </c>
       <c r="F14" t="n">
-        <v>0.036706105017073</v>
+        <v>0.04413999978842304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>svc_scaled</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.7649651610845732</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.02718938550859115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.115347204052946</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.01773307804396462</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>softvote_lr_gb_et</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8478313400198138</v>
+        <v>0.7964522450687794</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01592899719276268</v>
+        <v>0.02357988300216392</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3715476012769358</v>
+        <v>0.1853712976944825</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05069068522929388</v>
+        <v>0.05125696622536136</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7827777918629683</v>
+        <v>0.6846025597459205</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01875913928122007</v>
+        <v>0.02015002765830965</v>
       </c>
       <c r="E17" t="n">
-        <v>0.127235033139615</v>
+        <v>0.089148033989234</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03014154041782496</v>
+        <v>0.01336735536260493</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -862,22 +862,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7863515304731775</v>
+        <v>0.827086892166537</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01733311382267085</v>
+        <v>0.01245046370105388</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1545041028877369</v>
+        <v>0.3175058577634801</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03430388924934014</v>
+        <v>0.01428349135587473</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -886,22 +886,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7728757336611837</v>
+        <v>0.7567874192114911</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03233275904621683</v>
+        <v>0.02694376218237607</v>
       </c>
       <c r="E19" t="n">
-        <v>0.156249588301203</v>
+        <v>0.1268039870645716</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03979128816438763</v>
+        <v>0.01512300739831643</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7670100036804887</v>
+        <v>0.7344657829215215</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0258632371036844</v>
+        <v>0.02637591766024496</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1132699667646936</v>
+        <v>0.08889494131257136</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01648360830387073</v>
+        <v>0.0101205819623565</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -934,22 +934,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.795621952009657</v>
+        <v>0.777092038451736</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02262462673267423</v>
+        <v>0.02320676802473262</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1825062199655614</v>
+        <v>0.2548668559603268</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05066505875884924</v>
+        <v>0.02414689546435618</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6846025597459205</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02015002765830965</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.089148033989234</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01336735536260493</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.827086892166537</v>
+        <v>0.7645097964865715</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01245046370105388</v>
+        <v>0.01998253139500118</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3175058577634801</v>
+        <v>0.1256960788106765</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01428349135587473</v>
+        <v>0.0111111875630107</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7567874192114911</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02694376218237607</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1268039870645716</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01512300739831643</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7344657829215215</v>
+        <v>0.7544951316937933</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02637591766024496</v>
+        <v>0.01135738628816723</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08889494131257136</v>
+        <v>0.1182847363702429</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0101205819623565</v>
+        <v>0.00858114579579135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1054,22 +1054,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.777092038451736</v>
+        <v>0.7643554917214723</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02320676802473262</v>
+        <v>0.01846287389594341</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2548668559603268</v>
+        <v>0.1308379294871899</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02414689546435618</v>
+        <v>0.01051598906289089</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1078,22 +1078,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7436214385423241</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01760657006189662</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="E27" t="n">
-        <v>0.120027452177884</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01573639136082546</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.774496930153623</v>
+        <v>0.7883998687445136</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02248775545809407</v>
+        <v>0.008023982756139258</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1370758735728805</v>
+        <v>0.1983542113814164</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01332617412804189</v>
+        <v>0.02016621122068829</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1126,22 +1126,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7708916044891652</v>
+        <v>0.7753354867186564</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0192404102254878</v>
+        <v>0.01269043437239893</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1341677704487036</v>
+        <v>0.17448342405062</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01648410265468233</v>
+        <v>0.01082047555388005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7661750786398851</v>
+        <v>0.7519759936135035</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01321621587224425</v>
+        <v>0.01897235505529942</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1404056144694289</v>
+        <v>0.1604473928142211</v>
       </c>
       <c r="F30" t="n">
-        <v>0.009283179324686105</v>
+        <v>0.02469004502687826</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1174,22 +1174,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.7708481326343765</v>
+        <v>0.774307977615377</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01846386235785773</v>
+        <v>0.01587442623235423</v>
       </c>
       <c r="E31" t="n">
-        <v>0.13772014409709</v>
+        <v>0.1950261679377055</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01222979894217396</v>
+        <v>0.01799920717845304</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.740204074741885</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1222,22 +1222,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.7871773576552643</v>
+        <v>0.8560991058465504</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01052812384353352</v>
+        <v>0.01482657545051336</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1973119681773526</v>
+        <v>0.39299150315043</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0126853747689661</v>
+        <v>0.04328364565501456</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7735862526102607</v>
+        <v>0.8581412102778174</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01355371744243104</v>
+        <v>0.01343351241384613</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1759112725474974</v>
+        <v>0.3894527575943291</v>
       </c>
       <c r="F34" t="n">
-        <v>0.009687400006006397</v>
+        <v>0.04159488439462301</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1270,22 +1270,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7524403559136705</v>
+        <v>0.8341393621732202</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01815809526707301</v>
+        <v>0.0194148298495687</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1561432319098676</v>
+        <v>0.28501264267978</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02485627758998294</v>
+        <v>0.02798555356943055</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1294,136 +1294,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7729417717062963</v>
+        <v>0.859008083773802</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01696652667544666</v>
+        <v>0.01775204446314711</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1942662352121397</v>
+        <v>0.4019031011699147</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01901994907284056</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>logreg_l2_scaled</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.8380082807867801</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.02096671842468235</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.3626783404222963</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.036706105017073</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>gradboost</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.8574353556750157</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.01799383944150814</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.3886767546878503</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.03992927212471939</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>extratrees</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.8565860138008118</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.01338845306581416</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.3853073807126989</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.04225413424787459</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>svc_scaled</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.8352441775362471</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0196280256658652</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.2894366220528332</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.02287044597953614</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>softvote_lr_gb_et</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.8583037287540549</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.01749714474713204</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.3999103855990315</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.04408977752764391</v>
+        <v>0.05002623507853219</v>
       </c>
     </row>
   </sheetData>
@@ -1484,16 +1364,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.795621952009657</v>
+        <v>0.7964522450687794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02262462673267423</v>
+        <v>0.02357988300216392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1825062199655614</v>
+        <v>0.1853712976944825</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05066505875884924</v>
+        <v>0.05125696622536136</v>
       </c>
     </row>
     <row r="3">
@@ -1528,20 +1408,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7803300993572464</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02240333750729686</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1395906583983687</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01473078343769954</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="5">
@@ -1556,16 +1436,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
     <row r="6">
@@ -1580,16 +1460,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
   </sheetData>
@@ -1603,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1640,16 +1520,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7827777918629683</v>
+        <v>0.7830138502042437</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01875913928122007</v>
+        <v>0.01871381086800399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.127235033139615</v>
+        <v>0.1269362344566973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03014154041782496</v>
+        <v>0.03004361656874081</v>
       </c>
     </row>
     <row r="3">
@@ -1659,130 +1539,111 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7950423734525505</v>
+        <v>0.7914604990850014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.022906276421525</v>
+        <v>0.02177196714317657</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1921294753460224</v>
+        <v>0.1983569539223893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04173421597947816</v>
+        <v>0.0418411119299538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2_scaled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7749474054256495</v>
+        <v>0.7830138502042437</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03936580996781421</v>
+        <v>0.01871381086800399</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1888878873417933</v>
+        <v>0.1269362344566973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04243115752518334</v>
+        <v>0.03004361656874081</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logreg_l2_scaled</t>
+          <t>gradboost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7827777918629683</v>
+        <v>0.7865382823285895</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01875913928122007</v>
+        <v>0.02714716402184768</v>
       </c>
       <c r="D5" t="n">
-        <v>0.127235033139615</v>
+        <v>0.1635667006523789</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03014154041782496</v>
+        <v>0.04077642148042858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradboost</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7863515304731775</v>
+        <v>0.7735886016058289</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01733311382267085</v>
+        <v>0.03016234961409352</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1545041028877369</v>
+        <v>0.1643278581485317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03430388924934014</v>
+        <v>0.04413999978842304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>svc_scaled</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7728757336611837</v>
+        <v>0.7649651610845732</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03233275904621683</v>
+        <v>0.02718938550859115</v>
       </c>
       <c r="D7" t="n">
-        <v>0.156249588301203</v>
+        <v>0.115347204052946</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03979128816438763</v>
+        <v>0.01773307804396462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svc_scaled</t>
+          <t>softvote_lr_gb_et</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7670100036804887</v>
+        <v>0.7964522450687794</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0258632371036844</v>
+        <v>0.02357988300216392</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1132699667646936</v>
+        <v>0.1853712976944825</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01648360830387073</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>softvote_lr_gb_et</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.795621952009657</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.02262462673267423</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1825062199655614</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.05066505875884924</v>
+        <v>0.05125696622536136</v>
       </c>
     </row>
   </sheetData>
@@ -1796,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,114 +1728,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2_scaled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8193635515576089</v>
+        <v>0.6846025597459205</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02336584643623031</v>
+        <v>0.02015002765830965</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3434883471190159</v>
+        <v>0.089148033989234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02827551939034324</v>
+        <v>0.01336735536260493</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logreg_l2_scaled</t>
+          <t>gradboost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6846025597459205</v>
+        <v>0.827086892166537</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02015002765830965</v>
+        <v>0.01245046370105388</v>
       </c>
       <c r="D5" t="n">
-        <v>0.089148033989234</v>
+        <v>0.3175058577634801</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01336735536260493</v>
+        <v>0.01428349135587473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradboost</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.827086892166537</v>
+        <v>0.7567874192114911</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01245046370105388</v>
+        <v>0.02694376218237607</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3175058577634801</v>
+        <v>0.1268039870645716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01428349135587473</v>
+        <v>0.01512300739831643</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>svc_scaled</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7567874192114911</v>
+        <v>0.7344657829215215</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02694376218237607</v>
+        <v>0.02637591766024496</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1268039870645716</v>
+        <v>0.08889494131257136</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01512300739831643</v>
+        <v>0.0101205819623565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svc_scaled</t>
+          <t>softvote_lr_gb_et</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7344657829215215</v>
+        <v>0.777092038451736</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02637591766024496</v>
+        <v>0.02320676802473262</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08889494131257136</v>
+        <v>0.2548668559603268</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0101205819623565</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>softvote_lr_gb_et</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.777092038451736</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.02320676802473262</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.2548668559603268</v>
-      </c>
-      <c r="E9" t="n">
         <v>0.02414689546435618</v>
       </c>
     </row>
@@ -1989,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,16 +1868,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7436214385423241</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01760657006189662</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.120027452177884</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01573639136082546</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="3">
@@ -2045,130 +1887,111 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7803300993572464</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02240333750729686</v>
+        <v>0.01830461526364529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1395906583983687</v>
+        <v>0.1305084174604524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01473078343769954</v>
+        <v>0.01322728173796852</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2_scaled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7671712109690169</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01692627218546185</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1433738303844752</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01829340997248071</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logreg_l2_scaled</t>
+          <t>gradboost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7436214385423241</v>
+        <v>0.7645097964865715</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01760657006189662</v>
+        <v>0.01998253139500118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.120027452177884</v>
+        <v>0.1256960788106765</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01573639136082546</v>
+        <v>0.0111111875630107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradboost</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.774496930153623</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02248775545809407</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1370758735728805</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01332617412804189</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>svc_scaled</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7708916044891652</v>
+        <v>0.7544951316937933</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0192404102254878</v>
+        <v>0.01135738628816723</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1341677704487036</v>
+        <v>0.1182847363702429</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01648410265468233</v>
+        <v>0.00858114579579135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svc_scaled</t>
+          <t>softvote_lr_gb_et</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7661750786398851</v>
+        <v>0.7643554917214723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01321621587224425</v>
+        <v>0.01846287389594341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1404056144694289</v>
+        <v>0.1308379294871899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009283179324686105</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>softvote_lr_gb_et</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7708481326343765</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01846386235785773</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.13772014409709</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01222979894217396</v>
+        <v>0.01051598906289089</v>
       </c>
     </row>
   </sheetData>
@@ -2182,7 +2005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,16 +2042,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="3">
@@ -2238,130 +2061,111 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2_scaled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7950796888840379</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01567424950546039</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2118479711579678</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02546531256831987</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logreg_l2_scaled</t>
+          <t>gradboost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7883998687445136</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.008023982756139258</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.1983542113814164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.02016621122068829</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradboost</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7871773576552643</v>
+        <v>0.7753354867186564</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01052812384353352</v>
+        <v>0.01269043437239893</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1973119681773526</v>
+        <v>0.17448342405062</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0126853747689661</v>
+        <v>0.01082047555388005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>svc_scaled</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7735862526102607</v>
+        <v>0.7519759936135035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01355371744243104</v>
+        <v>0.01897235505529942</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1759112725474974</v>
+        <v>0.1604473928142211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009687400006006397</v>
+        <v>0.02469004502687826</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svc_scaled</t>
+          <t>softvote_lr_gb_et</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7524403559136705</v>
+        <v>0.774307977615377</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01815809526707301</v>
+        <v>0.01587442623235423</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1561432319098676</v>
+        <v>0.1950261679377055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02485627758998294</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>softvote_lr_gb_et</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.7729417717062963</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01696652667544666</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1942662352121397</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01901994907284056</v>
+        <v>0.01799920717845304</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2412,16 +2216,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="3">
@@ -2431,130 +2235,111 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>logreg_l2_scaled</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8478313400198138</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01592899719276268</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3715476012769358</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05069068522929388</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>logreg_l2_scaled</t>
+          <t>gradboost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8560991058465504</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.01482657545051336</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.39299150315043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.036706105017073</v>
+        <v>0.04328364565501456</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradboost</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8574353556750157</v>
+        <v>0.8581412102778174</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01799383944150814</v>
+        <v>0.01343351241384613</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3886767546878503</v>
+        <v>0.3894527575943291</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03992927212471939</v>
+        <v>0.04159488439462301</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>svc_scaled</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8565860138008118</v>
+        <v>0.8341393621732202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01338845306581416</v>
+        <v>0.0194148298495687</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3853073807126989</v>
+        <v>0.28501264267978</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04225413424787459</v>
+        <v>0.02798555356943055</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svc_scaled</t>
+          <t>softvote_lr_gb_et</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8352441775362471</v>
+        <v>0.859008083773802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0196280256658652</v>
+        <v>0.01775204446314711</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2894366220528332</v>
+        <v>0.4019031011699147</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02287044597953614</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>softvote_lr_gb_et</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8583037287540549</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01749714474713204</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.3999103855990315</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.04408977752764391</v>
+        <v>0.05002623507853219</v>
       </c>
     </row>
   </sheetData>

--- a/results/06_model_evaluation/05_ALL_model_eval.xlsx
+++ b/results/06_model_evaluation/05_ALL_model_eval.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7830138502042437</v>
+        <v>0.7827777918629683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01871381086800399</v>
+        <v>0.01875913928122007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1269362344566973</v>
+        <v>0.127235033139615</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03004361656874081</v>
+        <v>0.03014154041782496</v>
       </c>
     </row>
     <row r="3">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7914604990850014</v>
+        <v>0.7950423734525505</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02177196714317657</v>
+        <v>0.022906276421525</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1983569539223893</v>
+        <v>0.1921294753460224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0418411119299538</v>
+        <v>0.04173421597947816</v>
       </c>
     </row>
     <row r="4">
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7371297104138026</v>
+        <v>0.7416451769600094</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02055176014088759</v>
+        <v>0.01993688661995984</v>
       </c>
       <c r="E6" t="n">
-        <v>0.113979645704231</v>
+        <v>0.1154322800342247</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01327209032282319</v>
+        <v>0.01432159611287153</v>
       </c>
     </row>
     <row r="7">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7638655851081998</v>
+        <v>0.778291616922111</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01830461526364529</v>
+        <v>0.02016460778089968</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1305084174604524</v>
+        <v>0.1366611393084907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01322728173796852</v>
+        <v>0.01644375607216518</v>
       </c>
     </row>
     <row r="8">
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7423180768872754</v>
+        <v>0.740204074741885</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01740707860779314</v>
+        <v>0.01632377788364275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.150418939148557</v>
+        <v>0.1504672166943709</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01096860461154251</v>
+        <v>0.01174477485781384</v>
       </c>
     </row>
     <row r="9">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8102974592286788</v>
+        <v>0.8124041670509727</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008404306776686604</v>
+        <v>0.00960631081931577</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2163882894451978</v>
+        <v>0.2179801169523388</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01225359127876926</v>
+        <v>0.01386992304711891</v>
       </c>
     </row>
     <row r="10">
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8384060741259433</v>
+        <v>0.8380082807867801</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02144293790929938</v>
+        <v>0.02096671842468235</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3621556760174849</v>
+        <v>0.3626783404222963</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03892340905464424</v>
+        <v>0.036706105017073</v>
       </c>
     </row>
     <row r="11">
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8665735005647537</v>
+        <v>0.8635755888181507</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008279770287604037</v>
+        <v>0.007267449988741658</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4183159022170709</v>
+        <v>0.4197146136049616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05664601097712555</v>
+        <v>0.05043702845977172</v>
       </c>
     </row>
     <row r="12">
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7830138502042437</v>
+        <v>0.7827777918629683</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01871381086800399</v>
+        <v>0.01875913928122007</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1269362344566973</v>
+        <v>0.127235033139615</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03004361656874081</v>
+        <v>0.03014154041782496</v>
       </c>
     </row>
     <row r="13">
@@ -742,16 +742,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7865382823285895</v>
+        <v>0.7863515304731775</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02714716402184768</v>
+        <v>0.01733311382267085</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1635667006523789</v>
+        <v>0.1545041028877369</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04077642148042858</v>
+        <v>0.03430388924934014</v>
       </c>
     </row>
     <row r="14">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7735886016058289</v>
+        <v>0.7728757336611837</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03016234961409352</v>
+        <v>0.03233275904621683</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1643278581485317</v>
+        <v>0.156249588301203</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04413999978842304</v>
+        <v>0.03979128816438763</v>
       </c>
     </row>
     <row r="15">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7649651610845732</v>
+        <v>0.7670100036804887</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02718938550859115</v>
+        <v>0.0258632371036844</v>
       </c>
       <c r="E15" t="n">
-        <v>0.115347204052946</v>
+        <v>0.1132699667646936</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01773307804396462</v>
+        <v>0.01648360830387073</v>
       </c>
     </row>
     <row r="16">
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7964522450687794</v>
+        <v>0.795621952009657</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02357988300216392</v>
+        <v>0.02262462673267423</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1853712976944825</v>
+        <v>0.1825062199655614</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05125696622536136</v>
+        <v>0.05066505875884924</v>
       </c>
     </row>
     <row r="17">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7371297104138026</v>
+        <v>0.7416451769600094</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02055176014088759</v>
+        <v>0.01993688661995984</v>
       </c>
       <c r="E22" t="n">
-        <v>0.113979645704231</v>
+        <v>0.1154322800342247</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01327209032282319</v>
+        <v>0.01432159611287153</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7645097964865715</v>
+        <v>0.7753054223485613</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01998253139500118</v>
+        <v>0.01970127916584561</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1256960788106765</v>
+        <v>0.1352904023718657</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0111111875630107</v>
+        <v>0.01580335909372842</v>
       </c>
     </row>
     <row r="24">
@@ -1006,16 +1006,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7675390063081083</v>
+        <v>0.7706431402325833</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01865128568652915</v>
+        <v>0.01824097132401747</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1342371441199022</v>
+        <v>0.1348461163055937</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01543301317163794</v>
+        <v>0.01796663639692724</v>
       </c>
     </row>
     <row r="25">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7544951316937933</v>
+        <v>0.7602130881745923</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01135738628816723</v>
+        <v>0.01392039267849403</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1182847363702429</v>
+        <v>0.1381007774329141</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00858114579579135</v>
+        <v>0.006304980123472345</v>
       </c>
     </row>
     <row r="26">
@@ -1054,16 +1054,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7643554917214723</v>
+        <v>0.7683861628742591</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01846287389594341</v>
+        <v>0.01822216654225288</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1308379294871899</v>
+        <v>0.1372334173685621</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01051598906289089</v>
+        <v>0.01279874061212412</v>
       </c>
     </row>
     <row r="27">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7423180768872754</v>
+        <v>0.740204074741885</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01740707860779314</v>
+        <v>0.01632377788364275</v>
       </c>
       <c r="E27" t="n">
-        <v>0.150418939148557</v>
+        <v>0.1504672166943709</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01096860461154251</v>
+        <v>0.01174477485781384</v>
       </c>
     </row>
     <row r="28">
@@ -1102,16 +1102,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7883998687445136</v>
+        <v>0.7871773576552643</v>
       </c>
       <c r="D28" t="n">
-        <v>0.008023982756139258</v>
+        <v>0.01052812384353352</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1983542113814164</v>
+        <v>0.1973119681773526</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02016621122068829</v>
+        <v>0.0126853747689661</v>
       </c>
     </row>
     <row r="29">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7753354867186564</v>
+        <v>0.7735862526102607</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01269043437239893</v>
+        <v>0.01355371744243104</v>
       </c>
       <c r="E29" t="n">
-        <v>0.17448342405062</v>
+        <v>0.1759112725474974</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01082047555388005</v>
+        <v>0.009687400006006397</v>
       </c>
     </row>
     <row r="30">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7519759936135035</v>
+        <v>0.7524403559136705</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01897235505529942</v>
+        <v>0.01815809526707301</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1604473928142211</v>
+        <v>0.1561432319098676</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02469004502687826</v>
+        <v>0.02485627758998294</v>
       </c>
     </row>
     <row r="31">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.774307977615377</v>
+        <v>0.7729417717062963</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01587442623235423</v>
+        <v>0.01696652667544666</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1950261679377055</v>
+        <v>0.1942662352121397</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01799920717845304</v>
+        <v>0.01901994907284056</v>
       </c>
     </row>
     <row r="32">
@@ -1198,16 +1198,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.8384060741259433</v>
+        <v>0.8380082807867801</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02144293790929938</v>
+        <v>0.02096671842468235</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3621556760174849</v>
+        <v>0.3626783404222963</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03892340905464424</v>
+        <v>0.036706105017073</v>
       </c>
     </row>
     <row r="33">
@@ -1222,16 +1222,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.8560991058465504</v>
+        <v>0.8574353556750157</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01482657545051336</v>
+        <v>0.01799383944150814</v>
       </c>
       <c r="E33" t="n">
-        <v>0.39299150315043</v>
+        <v>0.3886767546878503</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04328364565501456</v>
+        <v>0.03992927212471939</v>
       </c>
     </row>
     <row r="34">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.8581412102778174</v>
+        <v>0.8565860138008118</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01343351241384613</v>
+        <v>0.01338845306581416</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3894527575943291</v>
+        <v>0.3853073807126989</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04159488439462301</v>
+        <v>0.04225413424787459</v>
       </c>
     </row>
     <row r="35">
@@ -1270,16 +1270,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.8341393621732202</v>
+        <v>0.8352441775362471</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0194148298495687</v>
+        <v>0.0196280256658652</v>
       </c>
       <c r="E35" t="n">
-        <v>0.28501264267978</v>
+        <v>0.2894366220528332</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02798555356943055</v>
+        <v>0.02287044597953614</v>
       </c>
     </row>
     <row r="36">
@@ -1294,16 +1294,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.859008083773802</v>
+        <v>0.8583037287540549</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01775204446314711</v>
+        <v>0.01749714474713204</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4019031011699147</v>
+        <v>0.3999103855990315</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05002623507853219</v>
+        <v>0.04408977752764391</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7964522450687794</v>
+        <v>0.795621952009657</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02357988300216392</v>
+        <v>0.02262462673267423</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1853712976944825</v>
+        <v>0.1825062199655614</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05125696622536136</v>
+        <v>0.05066505875884924</v>
       </c>
     </row>
     <row r="3">
@@ -1408,20 +1408,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>extratrees</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7675390063081083</v>
+        <v>0.778291616922111</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01865128568652915</v>
+        <v>0.02016460778089968</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1342371441199022</v>
+        <v>0.1366611393084907</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01543301317163794</v>
+        <v>0.01644375607216518</v>
       </c>
     </row>
     <row r="5">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8102974592286788</v>
+        <v>0.8124041670509727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008404306776686604</v>
+        <v>0.00960631081931577</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2163882894451978</v>
+        <v>0.2179801169523388</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01225359127876926</v>
+        <v>0.01386992304711891</v>
       </c>
     </row>
     <row r="6">
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8665735005647537</v>
+        <v>0.8635755888181507</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008279770287604037</v>
+        <v>0.007267449988741658</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4183159022170709</v>
+        <v>0.4197146136049616</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05664601097712555</v>
+        <v>0.05043702845977172</v>
       </c>
     </row>
   </sheetData>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7830138502042437</v>
+        <v>0.7827777918629683</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01871381086800399</v>
+        <v>0.01875913928122007</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1269362344566973</v>
+        <v>0.127235033139615</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03004361656874081</v>
+        <v>0.03014154041782496</v>
       </c>
     </row>
     <row r="3">
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7914604990850014</v>
+        <v>0.7950423734525505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02177196714317657</v>
+        <v>0.022906276421525</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1983569539223893</v>
+        <v>0.1921294753460224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0418411119299538</v>
+        <v>0.04173421597947816</v>
       </c>
     </row>
     <row r="4">
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7830138502042437</v>
+        <v>0.7827777918629683</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01871381086800399</v>
+        <v>0.01875913928122007</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1269362344566973</v>
+        <v>0.127235033139615</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03004361656874081</v>
+        <v>0.03014154041782496</v>
       </c>
     </row>
     <row r="5">
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7865382823285895</v>
+        <v>0.7863515304731775</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02714716402184768</v>
+        <v>0.01733311382267085</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1635667006523789</v>
+        <v>0.1545041028877369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04077642148042858</v>
+        <v>0.03430388924934014</v>
       </c>
     </row>
     <row r="6">
@@ -1596,16 +1596,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7735886016058289</v>
+        <v>0.7728757336611837</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03016234961409352</v>
+        <v>0.03233275904621683</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1643278581485317</v>
+        <v>0.156249588301203</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04413999978842304</v>
+        <v>0.03979128816438763</v>
       </c>
     </row>
     <row r="7">
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7649651610845732</v>
+        <v>0.7670100036804887</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02718938550859115</v>
+        <v>0.0258632371036844</v>
       </c>
       <c r="D7" t="n">
-        <v>0.115347204052946</v>
+        <v>0.1132699667646936</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01773307804396462</v>
+        <v>0.01648360830387073</v>
       </c>
     </row>
     <row r="8">
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7964522450687794</v>
+        <v>0.795621952009657</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02357988300216392</v>
+        <v>0.02262462673267423</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1853712976944825</v>
+        <v>0.1825062199655614</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05125696622536136</v>
+        <v>0.05066505875884924</v>
       </c>
     </row>
   </sheetData>
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7371297104138026</v>
+        <v>0.7416451769600094</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02055176014088759</v>
+        <v>0.01993688661995984</v>
       </c>
       <c r="D2" t="n">
-        <v>0.113979645704231</v>
+        <v>0.1154322800342247</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01327209032282319</v>
+        <v>0.01432159611287153</v>
       </c>
     </row>
     <row r="3">
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7638655851081998</v>
+        <v>0.778291616922111</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01830461526364529</v>
+        <v>0.02016460778089968</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1305084174604524</v>
+        <v>0.1366611393084907</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01322728173796852</v>
+        <v>0.01644375607216518</v>
       </c>
     </row>
     <row r="4">
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7371297104138026</v>
+        <v>0.7416451769600094</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02055176014088759</v>
+        <v>0.01993688661995984</v>
       </c>
       <c r="D4" t="n">
-        <v>0.113979645704231</v>
+        <v>0.1154322800342247</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01327209032282319</v>
+        <v>0.01432159611287153</v>
       </c>
     </row>
     <row r="5">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7645097964865715</v>
+        <v>0.7753054223485613</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01998253139500118</v>
+        <v>0.01970127916584561</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1256960788106765</v>
+        <v>0.1352904023718657</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0111111875630107</v>
+        <v>0.01580335909372842</v>
       </c>
     </row>
     <row r="6">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7675390063081083</v>
+        <v>0.7706431402325833</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01865128568652915</v>
+        <v>0.01824097132401747</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1342371441199022</v>
+        <v>0.1348461163055937</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01543301317163794</v>
+        <v>0.01796663639692724</v>
       </c>
     </row>
     <row r="7">
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7544951316937933</v>
+        <v>0.7602130881745923</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01135738628816723</v>
+        <v>0.01392039267849403</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1182847363702429</v>
+        <v>0.1381007774329141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00858114579579135</v>
+        <v>0.006304980123472345</v>
       </c>
     </row>
     <row r="8">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7643554917214723</v>
+        <v>0.7683861628742591</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01846287389594341</v>
+        <v>0.01822216654225288</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1308379294871899</v>
+        <v>0.1372334173685621</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01051598906289089</v>
+        <v>0.01279874061212412</v>
       </c>
     </row>
   </sheetData>
@@ -2042,16 +2042,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7423180768872754</v>
+        <v>0.740204074741885</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01740707860779314</v>
+        <v>0.01632377788364275</v>
       </c>
       <c r="D2" t="n">
-        <v>0.150418939148557</v>
+        <v>0.1504672166943709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01096860461154251</v>
+        <v>0.01174477485781384</v>
       </c>
     </row>
     <row r="3">
@@ -2061,16 +2061,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8102974592286788</v>
+        <v>0.8124041670509727</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008404306776686604</v>
+        <v>0.00960631081931577</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2163882894451978</v>
+        <v>0.2179801169523388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01225359127876926</v>
+        <v>0.01386992304711891</v>
       </c>
     </row>
     <row r="4">
@@ -2080,16 +2080,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7423180768872754</v>
+        <v>0.740204074741885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01740707860779314</v>
+        <v>0.01632377788364275</v>
       </c>
       <c r="D4" t="n">
-        <v>0.150418939148557</v>
+        <v>0.1504672166943709</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01096860461154251</v>
+        <v>0.01174477485781384</v>
       </c>
     </row>
     <row r="5">
@@ -2099,16 +2099,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7883998687445136</v>
+        <v>0.7871773576552643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008023982756139258</v>
+        <v>0.01052812384353352</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1983542113814164</v>
+        <v>0.1973119681773526</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02016621122068829</v>
+        <v>0.0126853747689661</v>
       </c>
     </row>
     <row r="6">
@@ -2118,16 +2118,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7753354867186564</v>
+        <v>0.7735862526102607</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01269043437239893</v>
+        <v>0.01355371744243104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.17448342405062</v>
+        <v>0.1759112725474974</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01082047555388005</v>
+        <v>0.009687400006006397</v>
       </c>
     </row>
     <row r="7">
@@ -2137,16 +2137,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7519759936135035</v>
+        <v>0.7524403559136705</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01897235505529942</v>
+        <v>0.01815809526707301</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1604473928142211</v>
+        <v>0.1561432319098676</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02469004502687826</v>
+        <v>0.02485627758998294</v>
       </c>
     </row>
     <row r="8">
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.774307977615377</v>
+        <v>0.7729417717062963</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01587442623235423</v>
+        <v>0.01696652667544666</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1950261679377055</v>
+        <v>0.1942662352121397</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01799920717845304</v>
+        <v>0.01901994907284056</v>
       </c>
     </row>
   </sheetData>
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8384060741259433</v>
+        <v>0.8380082807867801</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02144293790929938</v>
+        <v>0.02096671842468235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3621556760174849</v>
+        <v>0.3626783404222963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03892340905464424</v>
+        <v>0.036706105017073</v>
       </c>
     </row>
     <row r="3">
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8665735005647537</v>
+        <v>0.8635755888181507</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008279770287604037</v>
+        <v>0.007267449988741658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4183159022170709</v>
+        <v>0.4197146136049616</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05664601097712555</v>
+        <v>0.05043702845977172</v>
       </c>
     </row>
     <row r="4">
@@ -2254,16 +2254,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8384060741259433</v>
+        <v>0.8380082807867801</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02144293790929938</v>
+        <v>0.02096671842468235</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3621556760174849</v>
+        <v>0.3626783404222963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03892340905464424</v>
+        <v>0.036706105017073</v>
       </c>
     </row>
     <row r="5">
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8560991058465504</v>
+        <v>0.8574353556750157</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01482657545051336</v>
+        <v>0.01799383944150814</v>
       </c>
       <c r="D5" t="n">
-        <v>0.39299150315043</v>
+        <v>0.3886767546878503</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04328364565501456</v>
+        <v>0.03992927212471939</v>
       </c>
     </row>
     <row r="6">
@@ -2292,16 +2292,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8581412102778174</v>
+        <v>0.8565860138008118</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01343351241384613</v>
+        <v>0.01338845306581416</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3894527575943291</v>
+        <v>0.3853073807126989</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04159488439462301</v>
+        <v>0.04225413424787459</v>
       </c>
     </row>
     <row r="7">
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8341393621732202</v>
+        <v>0.8352441775362471</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0194148298495687</v>
+        <v>0.0196280256658652</v>
       </c>
       <c r="D7" t="n">
-        <v>0.28501264267978</v>
+        <v>0.2894366220528332</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02798555356943055</v>
+        <v>0.02287044597953614</v>
       </c>
     </row>
     <row r="8">
@@ -2330,16 +2330,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.859008083773802</v>
+        <v>0.8583037287540549</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01775204446314711</v>
+        <v>0.01749714474713204</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4019031011699147</v>
+        <v>0.3999103855990315</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05002623507853219</v>
+        <v>0.04408977752764391</v>
       </c>
     </row>
   </sheetData>
